--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_h_9.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_h_9.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.03351006058954598</v>
+        <v>0.02523046228346225</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008452235047349248</v>
+        <v>0.008438734620987253</v>
       </c>
       <c r="C2" t="n">
-        <v>56816802</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>56816802</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>37411885</v>
+        <v>3947707</v>
       </c>
       <c r="L2" t="n">
-        <v>19209269</v>
+        <v>1895871</v>
       </c>
       <c r="M2" t="n">
-        <v>4221860</v>
+        <v>392641</v>
       </c>
       <c r="N2" t="n">
-        <v>131299</v>
+        <v>11093</v>
       </c>
       <c r="O2" t="n">
-        <v>2574649</v>
+        <v>244829</v>
       </c>
       <c r="P2" t="n">
-        <v>1023086</v>
+        <v>98910</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999952912330627</v>
+        <v>0.9999963641166687</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8124145269393921</v>
+        <v>0.7661820650100708</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6424142718315125</v>
+        <v>0.5676374435424805</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5504482388496399</v>
+        <v>0.4595614075660706</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1495378315448761</v>
+        <v>0.1149652823805809</v>
       </c>
       <c r="V2" t="n">
-        <v>0.609233558177948</v>
+        <v>0.5211201310157776</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7187277674674988</v>
+        <v>0.631855309009552</v>
       </c>
       <c r="X2" t="n">
-        <v>56816802</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>56816802</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>43199395</v>
+        <v>4801660</v>
       </c>
       <c r="AG2" t="n">
-        <v>26831006</v>
+        <v>3018155</v>
       </c>
       <c r="AH2" t="n">
-        <v>7210544</v>
+        <v>805700</v>
       </c>
       <c r="AI2" t="n">
-        <v>531451</v>
+        <v>59334</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4136352</v>
+        <v>460847</v>
       </c>
       <c r="AK2" t="n">
-        <v>1621076</v>
+        <v>180323</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9560797214508057</v>
+        <v>0.9551666378974915</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9115321636199951</v>
+        <v>0.9119651317596436</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582335114479065</v>
+        <v>0.8582442998886108</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6618483662605286</v>
+        <v>0.660926342010498</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020155668258667</v>
+        <v>0.9019715189933777</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314467906951904</v>
+        <v>0.9314685463905334</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.008822077032829799</v>
+        <v>0.006336563773101055</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002026323576521127</v>
+        <v>0.002022102987121896</v>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>37411885</v>
+        <v>3947707</v>
       </c>
       <c r="E3" t="n">
-        <v>7390805</v>
+        <v>1014163</v>
       </c>
       <c r="F3" t="n">
-        <v>265384</v>
+        <v>45728</v>
       </c>
       <c r="G3" t="n">
-        <v>20604</v>
+        <v>3295</v>
       </c>
       <c r="H3" t="n">
-        <v>24504</v>
+        <v>3954</v>
       </c>
       <c r="I3" t="n">
-        <v>2420</v>
+        <v>376</v>
       </c>
       <c r="J3" t="n">
-        <v>90149331</v>
+        <v>10069597</v>
       </c>
       <c r="K3" t="n">
-        <v>93212415</v>
+        <v>10196041</v>
       </c>
       <c r="L3" t="n">
-        <v>106783796</v>
+        <v>11653144</v>
       </c>
       <c r="M3" t="n">
-        <v>135107705</v>
+        <v>15013623</v>
       </c>
       <c r="N3" t="n">
-        <v>145415911</v>
+        <v>16240726</v>
       </c>
       <c r="O3" t="n">
-        <v>140726482</v>
+        <v>15679615</v>
       </c>
       <c r="P3" t="n">
-        <v>144825210</v>
+        <v>16164685</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8292444944381714</v>
+        <v>0.7871443629264832</v>
       </c>
       <c r="S3" t="n">
-        <v>0.651378333568573</v>
+        <v>0.5712530016899109</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5019631385803223</v>
+        <v>0.4174207746982574</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1633567959070206</v>
+        <v>0.123424232006073</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5611065030097961</v>
+        <v>0.4787417352199554</v>
       </c>
       <c r="W3" t="n">
-        <v>0.58770751953125</v>
+        <v>0.5106719136238098</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>43199395</v>
+        <v>4801660</v>
       </c>
       <c r="Z3" t="n">
-        <v>1777968</v>
+        <v>198183</v>
       </c>
       <c r="AA3" t="n">
-        <v>76428</v>
+        <v>8469</v>
       </c>
       <c r="AB3" t="n">
-        <v>61298</v>
+        <v>6873</v>
       </c>
       <c r="AC3" t="n">
-        <v>269</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>270</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>90149598</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>99866284</v>
+        <v>11175395</v>
       </c>
       <c r="AG3" t="n">
-        <v>114872156</v>
+        <v>12805854</v>
       </c>
       <c r="AH3" t="n">
-        <v>137364636</v>
+        <v>15342287</v>
       </c>
       <c r="AI3" t="n">
-        <v>145891115</v>
+        <v>16295683</v>
       </c>
       <c r="AJ3" t="n">
-        <v>141928554</v>
+        <v>15854513</v>
       </c>
       <c r="AK3" t="n">
-        <v>145106283</v>
+        <v>16209047</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575262069702148</v>
+        <v>0.9574164748191833</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.909828245639801</v>
+        <v>0.9094131588935852</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8573063611984253</v>
+        <v>0.8565481305122375</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6612093448638916</v>
+        <v>0.6601688861846924</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014564752578735</v>
+        <v>0.9011460542678833</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312204718589783</v>
+        <v>0.931006908416748</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.07411824488879178</v>
+        <v>0.06138629626895008</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03197108341586186</v>
+        <v>0.03192845045564235</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>7986325</v>
+        <v>1106207</v>
       </c>
       <c r="E4" t="n">
-        <v>19209269</v>
+        <v>1895871</v>
       </c>
       <c r="F4" t="n">
-        <v>1897143</v>
+        <v>252105</v>
       </c>
       <c r="G4" t="n">
-        <v>109837</v>
+        <v>16990</v>
       </c>
       <c r="H4" t="n">
-        <v>255379</v>
+        <v>42047</v>
       </c>
       <c r="I4" t="n">
-        <v>32232</v>
+        <v>5574</v>
       </c>
       <c r="J4" t="n">
-        <v>267</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>8638357</v>
+        <v>1204733</v>
       </c>
       <c r="L4" t="n">
-        <v>10692416</v>
+        <v>1444062</v>
       </c>
       <c r="M4" t="n">
-        <v>3447998</v>
+        <v>461741</v>
       </c>
       <c r="N4" t="n">
-        <v>746733</v>
+        <v>85397</v>
       </c>
       <c r="O4" t="n">
-        <v>1651397</v>
+        <v>224984</v>
       </c>
       <c r="P4" t="n">
-        <v>400382</v>
+        <v>57629</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999976754188538</v>
+        <v>0.999998152256012</v>
       </c>
       <c r="R4" t="n">
-        <v>0.820743203163147</v>
+        <v>0.7765218019485474</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6468652486801147</v>
+        <v>0.5694394111633301</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5250888466835022</v>
+        <v>0.437478631734848</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1561421453952789</v>
+        <v>0.1190446689724922</v>
       </c>
       <c r="V4" t="n">
-        <v>0.584180474281311</v>
+        <v>0.4990328848361969</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6466477513313293</v>
+        <v>0.564836859703064</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1853220</v>
+        <v>210622</v>
       </c>
       <c r="Z4" t="n">
-        <v>26831006</v>
+        <v>3018155</v>
       </c>
       <c r="AA4" t="n">
-        <v>745446</v>
+        <v>83217</v>
       </c>
       <c r="AB4" t="n">
-        <v>49654</v>
+        <v>5601</v>
       </c>
       <c r="AC4" t="n">
-        <v>10250</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>612</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1984488</v>
+        <v>225379</v>
       </c>
       <c r="AG4" t="n">
-        <v>2604056</v>
+        <v>291352</v>
       </c>
       <c r="AH4" t="n">
-        <v>1191067</v>
+        <v>133077</v>
       </c>
       <c r="AI4" t="n">
-        <v>271529</v>
+        <v>30440</v>
       </c>
       <c r="AJ4" t="n">
-        <v>449325</v>
+        <v>50086</v>
       </c>
       <c r="AK4" t="n">
-        <v>119309</v>
+        <v>13267</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9568024277687073</v>
+        <v>0.9562901854515076</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106794595718384</v>
+        <v>0.9106873869895935</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8577696084976196</v>
+        <v>0.857395350933075</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6615287065505981</v>
+        <v>0.6605474352836609</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017359018325806</v>
+        <v>0.9015586376190186</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.931333601474762</v>
+        <v>0.9312376976013184</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>467460</v>
+        <v>72882</v>
       </c>
       <c r="E5" t="n">
-        <v>2669403</v>
+        <v>334082</v>
       </c>
       <c r="F5" t="n">
-        <v>4221860</v>
+        <v>392641</v>
       </c>
       <c r="G5" t="n">
-        <v>242340</v>
+        <v>27964</v>
       </c>
       <c r="H5" t="n">
-        <v>716419</v>
+        <v>98358</v>
       </c>
       <c r="I5" t="n">
-        <v>93198</v>
+        <v>14706</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7703743</v>
+        <v>1067519</v>
       </c>
       <c r="L5" t="n">
-        <v>10280919</v>
+        <v>1422923</v>
       </c>
       <c r="M5" t="n">
-        <v>4188837</v>
+        <v>547995</v>
       </c>
       <c r="N5" t="n">
-        <v>672457</v>
+        <v>78784</v>
       </c>
       <c r="O5" t="n">
-        <v>2013872</v>
+        <v>266572</v>
       </c>
       <c r="P5" t="n">
-        <v>717722</v>
+        <v>94776</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999982118606567</v>
+        <v>0.9999985694885254</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8888038396835327</v>
+        <v>0.8615831136703491</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8572916388511658</v>
+        <v>0.8253542184829712</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9480368494987488</v>
+        <v>0.9384907484054565</v>
       </c>
       <c r="U5" t="n">
-        <v>0.990343451499939</v>
+        <v>0.9899986982345581</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9750605225563049</v>
+        <v>0.9700562953948975</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9923921227455139</v>
+        <v>0.9907160401344299</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>72334</v>
+        <v>8120</v>
       </c>
       <c r="Z5" t="n">
-        <v>769884</v>
+        <v>86892</v>
       </c>
       <c r="AA5" t="n">
-        <v>7210544</v>
+        <v>805700</v>
       </c>
       <c r="AB5" t="n">
-        <v>89719</v>
+        <v>10028</v>
       </c>
       <c r="AC5" t="n">
-        <v>262519</v>
+        <v>29263</v>
       </c>
       <c r="AD5" t="n">
-        <v>5697</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1916233</v>
+        <v>213566</v>
       </c>
       <c r="AG5" t="n">
-        <v>2659182</v>
+        <v>300639</v>
       </c>
       <c r="AH5" t="n">
-        <v>1200153</v>
+        <v>134936</v>
       </c>
       <c r="AI5" t="n">
-        <v>272305</v>
+        <v>30543</v>
       </c>
       <c r="AJ5" t="n">
-        <v>452169</v>
+        <v>50554</v>
       </c>
       <c r="AK5" t="n">
-        <v>119732</v>
+        <v>13363</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734584093093872</v>
+        <v>0.9732611179351807</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641875028610229</v>
+        <v>0.9639381766319275</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837294816970825</v>
+        <v>0.9836736917495728</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962996244430542</v>
+        <v>0.9962851405143738</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.993865966796875</v>
+        <v>0.993869423866272</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983735084533691</v>
+        <v>0.998377799987793</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>138573</v>
+        <v>17556</v>
       </c>
       <c r="E6" t="n">
-        <v>198452</v>
+        <v>24258</v>
       </c>
       <c r="F6" t="n">
-        <v>229675</v>
+        <v>23816</v>
       </c>
       <c r="G6" t="n">
-        <v>131299</v>
+        <v>11093</v>
       </c>
       <c r="H6" t="n">
-        <v>93615</v>
+        <v>11350</v>
       </c>
       <c r="I6" t="n">
-        <v>12085</v>
+        <v>1795</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>58491</v>
+        <v>6601</v>
       </c>
       <c r="Z6" t="n">
-        <v>48185</v>
+        <v>5386</v>
       </c>
       <c r="AA6" t="n">
-        <v>98390</v>
+        <v>11048</v>
       </c>
       <c r="AB6" t="n">
-        <v>531451</v>
+        <v>59334</v>
       </c>
       <c r="AC6" t="n">
-        <v>62910</v>
+        <v>7027</v>
       </c>
       <c r="AD6" t="n">
-        <v>4329</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>43705</v>
+        <v>7868</v>
       </c>
       <c r="E7" t="n">
-        <v>394831</v>
+        <v>64553</v>
       </c>
       <c r="F7" t="n">
-        <v>971607</v>
+        <v>126379</v>
       </c>
       <c r="G7" t="n">
-        <v>343227</v>
+        <v>32594</v>
       </c>
       <c r="H7" t="n">
-        <v>2574649</v>
+        <v>244829</v>
       </c>
       <c r="I7" t="n">
-        <v>260447</v>
+        <v>35178</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>191</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>7290</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>267822</v>
+        <v>30010</v>
       </c>
       <c r="AB7" t="n">
-        <v>68465</v>
+        <v>7671</v>
       </c>
       <c r="AC7" t="n">
-        <v>4136352</v>
+        <v>460847</v>
       </c>
       <c r="AD7" t="n">
-        <v>108401</v>
+        <v>12055</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>109</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>2294</v>
+        <v>220</v>
       </c>
       <c r="E8" t="n">
-        <v>38925</v>
+        <v>7006</v>
       </c>
       <c r="F8" t="n">
-        <v>84189</v>
+        <v>13713</v>
       </c>
       <c r="G8" t="n">
-        <v>30725</v>
+        <v>4554</v>
       </c>
       <c r="H8" t="n">
-        <v>561480</v>
+        <v>69275</v>
       </c>
       <c r="I8" t="n">
-        <v>1023086</v>
+        <v>98910</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>252</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>729</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2981</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2393</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>113377</v>
+        <v>12654</v>
       </c>
       <c r="AD8" t="n">
-        <v>1621076</v>
+        <v>180323</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
